--- a/assets/Game/DataTables/Excel/DataTable.xlsx
+++ b/assets/Game/DataTables/Excel/DataTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="19095" windowHeight="9045" tabRatio="785" activeTab="2"/>
+    <workbookView windowWidth="19095" windowHeight="9045" tabRatio="785" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Entity" sheetId="4" r:id="rId1"/>
@@ -12,13 +12,14 @@
     <sheet name="Sound" sheetId="10" r:id="rId3"/>
     <sheet name="Scene" sheetId="9" r:id="rId4"/>
     <sheet name="UISound" sheetId="13" r:id="rId5"/>
+    <sheet name="Player" sheetId="14" r:id="rId6"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84">
   <si>
     <t>#</t>
   </si>
@@ -231,6 +232,45 @@
   </si>
   <si>
     <t>click</t>
+  </si>
+  <si>
+    <t>MaxHp</t>
+  </si>
+  <si>
+    <t>MoveSpeed</t>
+  </si>
+  <si>
+    <t>SprintSpeedScale</t>
+  </si>
+  <si>
+    <t>JumpSpeed</t>
+  </si>
+  <si>
+    <t>DefaultWeaponId</t>
+  </si>
+  <si>
+    <t>MaxWeaponSlots</t>
+  </si>
+  <si>
+    <t>玩家id</t>
+  </si>
+  <si>
+    <t>最大生命值</t>
+  </si>
+  <si>
+    <t>行走速度（单位/秒）</t>
+  </si>
+  <si>
+    <t>冲刺倍率（Shift 键）；最终速度 = MoveSpeed × 该值</t>
+  </si>
+  <si>
+    <t>跳跃初速度</t>
+  </si>
+  <si>
+    <t>出生时持有的武器，对应后续 DRWeapon.id</t>
+  </si>
+  <si>
+    <t>最多同时携带的武器数量</t>
   </si>
 </sst>
 </file>
@@ -238,12 +278,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -252,15 +292,28 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="9.75"/>
+      <color rgb="FFCCCCCC"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9.75"/>
+      <color rgb="FFCCCCCC"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -273,6 +326,69 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
@@ -280,9 +396,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -297,70 +412,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -383,14 +443,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -405,13 +458,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -423,7 +560,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -436,156 +639,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -596,6 +649,26 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -614,11 +687,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -627,7 +706,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -643,21 +722,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -685,17 +749,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -704,10 +757,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -716,141 +769,147 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1929,4 +1988,128 @@
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" ht="14.25" spans="1:9">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25" spans="1:9">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>100</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
+  <headerFooter/>
+</worksheet>
 </file>